--- a/backend/real_data/subjects_information_3.xlsx
+++ b/backend/real_data/subjects_information_3.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\school_timeTable_v1.9\backend\real_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\school_timeTable_v2.0\backend\real_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E20D0C-668E-4686-9048-09BB3B44F05A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA4F86E-080C-458F-95D8-E8783BE274DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="115">
   <si>
     <t>Tên Môn Học</t>
   </si>
@@ -347,6 +347,24 @@
   </si>
   <si>
     <t>CNNN11</t>
+  </si>
+  <si>
+    <t>Sinh Hoạt Lớp 10</t>
+  </si>
+  <si>
+    <t>SHL10</t>
+  </si>
+  <si>
+    <t>Sinh Hoạt Lớp 11</t>
+  </si>
+  <si>
+    <t>SHL11</t>
+  </si>
+  <si>
+    <t>Sinh Hoạt Lớp 12</t>
+  </si>
+  <si>
+    <t>SHL12</t>
   </si>
 </sst>
 </file>
@@ -403,12 +421,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -713,7 +737,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31.44140625" customWidth="1"/>
@@ -753,43 +777,39 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="E2" t="s">
-        <v>106</v>
-      </c>
-      <c r="F2" t="s">
-        <v>106</v>
-      </c>
-      <c r="G2" t="s">
-        <v>101</v>
-      </c>
-      <c r="H2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A2" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" s="4">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3" t="s">
         <v>106</v>
       </c>
       <c r="F3" t="s">
         <v>106</v>
+      </c>
+      <c r="G3" t="s">
+        <v>101</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -797,13 +817,13 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" t="s">
         <v>106</v>
@@ -817,19 +837,19 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="s">
         <v>106</v>
       </c>
-      <c r="G5" t="s">
-        <v>103</v>
+      <c r="F5" t="s">
+        <v>106</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -837,16 +857,19 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
       <c r="E6" t="s">
         <v>106</v>
+      </c>
+      <c r="G6" t="s">
+        <v>103</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -854,13 +877,13 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="s">
         <v>106</v>
@@ -871,10 +894,10 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -888,36 +911,33 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
+        <v>106</v>
+      </c>
+      <c r="H9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B10" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C9">
-        <v>2</v>
-      </c>
-      <c r="E9" t="s">
-        <v>106</v>
-      </c>
-      <c r="H9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>39</v>
-      </c>
       <c r="C10">
         <v>2</v>
       </c>
       <c r="E10" t="s">
-        <v>107</v>
-      </c>
-      <c r="G10" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -925,10 +945,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -945,16 +965,19 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C12">
         <v>2</v>
       </c>
       <c r="E12" t="s">
         <v>107</v>
+      </c>
+      <c r="G12" t="s">
+        <v>102</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -962,10 +985,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -979,10 +1002,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C14">
         <v>2</v>
@@ -996,10 +1019,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>93</v>
+        <v>46</v>
       </c>
       <c r="B15" t="s">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="C15">
         <v>2</v>
@@ -1013,73 +1036,58 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>93</v>
+      </c>
+      <c r="B16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="E16" t="s">
+        <v>107</v>
+      </c>
+      <c r="H16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>13</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B17" t="s">
         <v>92</v>
       </c>
-      <c r="C16">
-        <v>2</v>
-      </c>
-      <c r="E16" t="s">
-        <v>107</v>
-      </c>
-      <c r="G16" t="s">
+      <c r="C17">
+        <v>2</v>
+      </c>
+      <c r="E17" t="s">
+        <v>107</v>
+      </c>
+      <c r="G17" t="s">
         <v>102</v>
       </c>
-      <c r="H16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C17">
-        <v>3</v>
-      </c>
-      <c r="E17" t="s">
-        <v>106</v>
-      </c>
-      <c r="F17" t="s">
-        <v>106</v>
-      </c>
-      <c r="G17" t="s">
-        <v>100</v>
-      </c>
       <c r="H17" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C18">
-        <v>4</v>
-      </c>
-      <c r="E18" t="s">
-        <v>106</v>
-      </c>
-      <c r="F18" t="s">
-        <v>106</v>
-      </c>
-      <c r="H18" t="s">
-        <v>8</v>
+      <c r="A18" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C18" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C19">
         <v>3</v>
@@ -1090,25 +1098,28 @@
       <c r="F19" t="s">
         <v>106</v>
       </c>
+      <c r="G19" t="s">
+        <v>100</v>
+      </c>
       <c r="H19" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E20" t="s">
         <v>106</v>
       </c>
-      <c r="G20" t="s">
-        <v>105</v>
+      <c r="F20" t="s">
+        <v>106</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -1116,15 +1127,18 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E21" t="s">
+        <v>106</v>
+      </c>
+      <c r="F21" t="s">
         <v>106</v>
       </c>
       <c r="H21" t="s">
@@ -1133,16 +1147,19 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" t="s">
         <v>106</v>
+      </c>
+      <c r="G22" t="s">
+        <v>105</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1150,10 +1167,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -1167,56 +1184,50 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="E24" t="s">
+        <v>106</v>
+      </c>
+      <c r="H24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="E25" t="s">
+        <v>106</v>
+      </c>
+      <c r="H25" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B26" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C24">
-        <v>2</v>
-      </c>
-      <c r="E24" t="s">
-        <v>106</v>
-      </c>
-      <c r="H24" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>18</v>
-      </c>
-      <c r="B25" t="s">
-        <v>68</v>
-      </c>
-      <c r="C25">
-        <v>2</v>
-      </c>
-      <c r="E25" t="s">
-        <v>107</v>
-      </c>
-      <c r="G25" t="s">
-        <v>102</v>
-      </c>
-      <c r="H25" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>19</v>
-      </c>
-      <c r="B26" t="s">
-        <v>69</v>
-      </c>
       <c r="C26">
         <v>2</v>
       </c>
       <c r="E26" t="s">
-        <v>107</v>
-      </c>
-      <c r="G26" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1224,10 +1235,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C27">
         <v>2</v>
@@ -1244,16 +1255,19 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B28" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C28">
         <v>2</v>
       </c>
       <c r="E28" t="s">
         <v>107</v>
+      </c>
+      <c r="G28" t="s">
+        <v>102</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1261,16 +1275,19 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="B29" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C29">
         <v>2</v>
       </c>
       <c r="E29" t="s">
         <v>107</v>
+      </c>
+      <c r="G29" t="s">
+        <v>102</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1278,10 +1295,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>95</v>
+        <v>26</v>
       </c>
       <c r="B30" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="C30">
         <v>2</v>
@@ -1295,10 +1312,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="B31" t="s">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="C31">
         <v>2</v>
@@ -1312,102 +1329,84 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>95</v>
+      </c>
+      <c r="B32" t="s">
+        <v>96</v>
+      </c>
+      <c r="C32">
+        <v>2</v>
+      </c>
+      <c r="E32" t="s">
+        <v>107</v>
+      </c>
+      <c r="H32" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>99</v>
+      </c>
+      <c r="B33" t="s">
+        <v>108</v>
+      </c>
+      <c r="C33">
+        <v>2</v>
+      </c>
+      <c r="E33" t="s">
+        <v>107</v>
+      </c>
+      <c r="H33" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>22</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B34" t="s">
         <v>91</v>
       </c>
-      <c r="C32">
-        <v>2</v>
-      </c>
-      <c r="E32" t="s">
-        <v>107</v>
-      </c>
-      <c r="G32" t="s">
+      <c r="C34">
+        <v>2</v>
+      </c>
+      <c r="E34" t="s">
+        <v>107</v>
+      </c>
+      <c r="G34" t="s">
         <v>102</v>
       </c>
-      <c r="H32" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C33">
-        <v>4</v>
-      </c>
-      <c r="E33" t="s">
-        <v>106</v>
-      </c>
-      <c r="F33" t="s">
-        <v>106</v>
-      </c>
-      <c r="H33" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C34">
-        <v>3</v>
-      </c>
-      <c r="E34" t="s">
-        <v>106</v>
-      </c>
-      <c r="F34" t="s">
-        <v>106</v>
-      </c>
-      <c r="G34" t="s">
-        <v>100</v>
-      </c>
       <c r="H34" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C35">
-        <v>3</v>
-      </c>
-      <c r="E35" t="s">
-        <v>106</v>
-      </c>
-      <c r="F35" t="s">
-        <v>106</v>
-      </c>
-      <c r="H35" t="s">
-        <v>8</v>
+      <c r="A35" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C35" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="C36">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E36" t="s">
         <v>106</v>
       </c>
-      <c r="G36" t="s">
-        <v>104</v>
+      <c r="F36" t="s">
+        <v>106</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1415,16 +1414,22 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E37" t="s">
         <v>106</v>
+      </c>
+      <c r="F37" t="s">
+        <v>106</v>
+      </c>
+      <c r="G37" t="s">
+        <v>100</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1432,15 +1437,18 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E38" t="s">
+        <v>106</v>
+      </c>
+      <c r="F38" t="s">
         <v>106</v>
       </c>
       <c r="H38" t="s">
@@ -1449,16 +1457,19 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39" t="s">
         <v>106</v>
+      </c>
+      <c r="G39" t="s">
+        <v>104</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1466,73 +1477,67 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+      <c r="E40" t="s">
+        <v>106</v>
+      </c>
+      <c r="H40" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C41">
+        <v>2</v>
+      </c>
+      <c r="E41" t="s">
+        <v>106</v>
+      </c>
+      <c r="H41" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="E42" t="s">
+        <v>106</v>
+      </c>
+      <c r="H42" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B43" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C40">
-        <v>2</v>
-      </c>
-      <c r="E40" t="s">
-        <v>106</v>
-      </c>
-      <c r="H40" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>28</v>
-      </c>
-      <c r="B41" t="s">
-        <v>84</v>
-      </c>
-      <c r="C41">
-        <v>2</v>
-      </c>
-      <c r="E41" t="s">
-        <v>107</v>
-      </c>
-      <c r="G41" t="s">
-        <v>102</v>
-      </c>
-      <c r="H41" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>29</v>
-      </c>
-      <c r="B42" t="s">
-        <v>85</v>
-      </c>
-      <c r="C42">
-        <v>2</v>
-      </c>
-      <c r="E42" t="s">
-        <v>107</v>
-      </c>
-      <c r="G42" t="s">
-        <v>102</v>
-      </c>
-      <c r="H42" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>33</v>
-      </c>
-      <c r="B43" t="s">
-        <v>86</v>
-      </c>
       <c r="C43">
         <v>2</v>
       </c>
       <c r="E43" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1540,16 +1545,19 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B44" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C44">
         <v>2</v>
       </c>
       <c r="E44" t="s">
         <v>107</v>
+      </c>
+      <c r="G44" t="s">
+        <v>102</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1557,16 +1565,19 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="B45" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C45">
         <v>2</v>
       </c>
       <c r="E45" t="s">
         <v>107</v>
+      </c>
+      <c r="G45" t="s">
+        <v>102</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1574,10 +1585,10 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>97</v>
+        <v>33</v>
       </c>
       <c r="B46" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="C46">
         <v>2</v>
@@ -1591,21 +1602,72 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
+        <v>36</v>
+      </c>
+      <c r="B47" t="s">
+        <v>87</v>
+      </c>
+      <c r="C47">
+        <v>2</v>
+      </c>
+      <c r="E47" t="s">
+        <v>107</v>
+      </c>
+      <c r="H47" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>88</v>
+      </c>
+      <c r="B48" t="s">
+        <v>89</v>
+      </c>
+      <c r="C48">
+        <v>2</v>
+      </c>
+      <c r="E48" t="s">
+        <v>107</v>
+      </c>
+      <c r="H48" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>97</v>
+      </c>
+      <c r="B49" t="s">
+        <v>98</v>
+      </c>
+      <c r="C49">
+        <v>2</v>
+      </c>
+      <c r="E49" t="s">
+        <v>107</v>
+      </c>
+      <c r="H49" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
         <v>32</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B50" t="s">
         <v>90</v>
       </c>
-      <c r="C47">
-        <v>2</v>
-      </c>
-      <c r="E47" t="s">
-        <v>107</v>
-      </c>
-      <c r="G47" t="s">
+      <c r="C50">
+        <v>2</v>
+      </c>
+      <c r="E50" t="s">
+        <v>107</v>
+      </c>
+      <c r="G50" t="s">
         <v>102</v>
       </c>
-      <c r="H47" t="s">
+      <c r="H50" t="s">
         <v>8</v>
       </c>
     </row>
